--- a/static/template.xlsx
+++ b/static/template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00856904"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +58,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="004361EE"/>
         <bgColor rgb="004361EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -92,6 +101,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -166,6 +178,41 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Deal Manager</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>可留空：填 Amazon Link 后系统自动抓取</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>可留空：填 Amazon Link 后系统自动抓取</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>填写后，Image URL / Original Price / Rating / Review Count 可留空自动抓取</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>可留空：填 Amazon Link 后系统自动抓取</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>可留空：填 Amazon Link 后系统自动抓取</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -457,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -471,39 +518,64 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Fill in deals</t>
+          <t>1. 填表</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Go to Deals sheet. Only Name is required.</t>
+          <t>在 Deals 表填写。仅 Name 必填，其余列可留空。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2. Save</t>
+          <t>2. Amazon Link 自动抓取</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Save as .xlsx.</t>
+          <t>填了 Amazon Link 后，Image URL / Original Price / Rating / Review Count 四列可留空——导入时勾选"自动抓取"，系统会自动抓取 Amazon 现价、星级、评论数和图片。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3. Upload</t>
+          <t>3. 手动补全</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Admin &gt; Import &gt; Upload Excel File &gt; select this file.</t>
+          <t>导入后也可在列表页勾选 deal，点"补全 Amazon 数据"按钮，自动补全所有空白字段（不覆盖已有数据）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4. 保存</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>另存为 .xlsx。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5. 上传</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Admin &gt; Import &gt; Upload Excel File &gt; 选择此文件。</t>
         </is>
       </c>
     </row>
@@ -567,12 +639,12 @@
           <t>CC ID</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Original Price</t>
         </is>
@@ -607,12 +679,12 @@
           <t>Promotion Link</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -871,5 +943,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>